--- a/reports/二级子公司D_现金流量表_2026-05.xlsx
+++ b/reports/二级子公司D_现金流量表_2026-05.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>74475180</v>
+        <v>72168403</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>346345740</v>
+        <v>335874824</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>1478741</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>6883763</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>740075</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>3432544</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>368545</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>1720873</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>296817</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>1373456</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>220692</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>1031941</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>148565</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>687245</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>110342</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>515527</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>74210</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>343926</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>184253</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>858517</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>92995</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>432392</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>58763</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>272848</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>190962</v>
+        <v>185069</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>888066</v>
+        <v>863382</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>1273080</v>
+        <v>1239934</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>5920440</v>
+        <v>5740914</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>75939222</v>
+        <v>77367404</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>48801400</v>
+        <v>47205565</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>226950200</v>
+        <v>220186133</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>493939</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>2293927</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>369237</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>1716452</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>246196</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>1147353</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>185202</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>858175</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>122748</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>573548</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>93283</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>431497</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>7638480</v>
+        <v>7379209</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>35522640</v>
+        <v>34503946</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>4031420</v>
+        <v>3933181</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>18748060</v>
+        <v>18201613</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1591350</v>
+        <v>1538314</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>7400550</v>
+        <v>7181968</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>62062650</v>
+        <v>61566874</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>13876572</v>
+        <v>15800530</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>82400</v>
+        <v>79623</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>412000</v>
+        <v>400359</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>721000</v>
+        <v>696663</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>3605000</v>
+        <v>3500419</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>432600</v>
+        <v>421696</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>2163000</v>
+        <v>2100655</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>803400</v>
+        <v>776286</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>8240000</v>
+        <v>8011456</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>41200000</v>
+        <v>40041413</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>1236000</v>
+        <v>1200206</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>6180000</v>
+        <v>5992490</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>5665000</v>
+        <v>5490336</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>28325000</v>
+        <v>27536772</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>185400</v>
+        <v>179103</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>927000</v>
+        <v>900365</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>8425400</v>
+        <v>8190559</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-7622000</v>
+        <v>-7414273</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1545000</v>
+        <v>1498626</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>7725000</v>
+        <v>7491606</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2575000</v>
+        <v>2505608</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>12875000</v>
+        <v>12483315</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2575000</v>
+        <v>2491120</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>12875000</v>
+        <v>12515441</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>82400</v>
+        <v>80359</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>412000</v>
+        <v>399598</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>4202400</v>
+        <v>4084593</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>2060000</v>
+        <v>2009813</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>10300000</v>
+        <v>9997315</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>2060000</v>
+        <v>1991314</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>10300000</v>
+        <v>9998361</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>329600</v>
+        <v>321064</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>1648000</v>
+        <v>1600925</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>288400</v>
+        <v>280109</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>1442000</v>
+        <v>1401667</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>41200</v>
+        <v>40049</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>206000</v>
+        <v>199736</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>2430800</v>
+        <v>2370926</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>1771600</v>
+        <v>1713667</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>8026172</v>
+        <v>10099924</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>8026172</v>
+        <v>10099924</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
